--- a/artfynd/A 23563-2023 artfynd.xlsx
+++ b/artfynd/A 23563-2023 artfynd.xlsx
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125320479</v>
+        <v>125320520</v>
       </c>
       <c r="B3" t="n">
-        <v>56404</v>
+        <v>56411</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,30 +825,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -858,11 +858,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -920,11 +916,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>04:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>15 registreringar med sång, stort antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -951,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125320520</v>
+        <v>125320479</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
+        <v>56404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,30 +954,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -996,7 +987,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -1054,6 +1049,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>15 registreringar med sång, stort antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 23563-2023 artfynd.xlsx
+++ b/artfynd/A 23563-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125320553</v>
+        <v>125320520</v>
       </c>
       <c r="B2" t="n">
-        <v>56423</v>
+        <v>56411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,11 +720,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -782,11 +778,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>04:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>6 registreringar av sång, ett antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125320520</v>
+        <v>125320479</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
+        <v>56404</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,30 +816,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -858,7 +849,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -916,6 +911,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>15 registreringar med sång, stort antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125320479</v>
+        <v>125320553</v>
       </c>
       <c r="B4" t="n">
-        <v>56404</v>
+        <v>56423</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,30 +954,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>15 registreringar med sång, stort antal födosöksbeteenden.</t>
+          <t>6 registreringar av sång, ett antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 23563-2023 artfynd.xlsx
+++ b/artfynd/A 23563-2023 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125320479</v>
+        <v>125320553</v>
       </c>
       <c r="B3" t="n">
-        <v>56404</v>
+        <v>56423</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,30 +816,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>15 registreringar med sång, stort antal födosöksbeteenden.</t>
+          <t>6 registreringar av sång, ett antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125320553</v>
+        <v>125320479</v>
       </c>
       <c r="B4" t="n">
-        <v>56423</v>
+        <v>56404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,30 +954,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>6 registreringar av sång, ett antal födosöksbeteenden.</t>
+          <t>15 registreringar med sång, stort antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 23563-2023 artfynd.xlsx
+++ b/artfynd/A 23563-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125320520</v>
+        <v>125320479</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
+        <v>56518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -778,6 +782,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>15 registreringar med sång, stort antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125320553</v>
+        <v>125320520</v>
       </c>
       <c r="B3" t="n">
-        <v>56423</v>
+        <v>56525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,26 +829,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,11 +858,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -911,11 +916,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>04:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>6 registreringar av sång, ett antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125320479</v>
+        <v>125320553</v>
       </c>
       <c r="B4" t="n">
-        <v>56404</v>
+        <v>56537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,30 +954,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>15 registreringar med sång, stort antal födosöksbeteenden.</t>
+          <t>6 registreringar av sång, ett antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 23563-2023 artfynd.xlsx
+++ b/artfynd/A 23563-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125320479</v>
+        <v>125320553</v>
       </c>
       <c r="B2" t="n">
-        <v>56518</v>
+        <v>56537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>15 registreringar med sång, stort antal födosöksbeteenden.</t>
+          <t>6 registreringar av sång, ett antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -942,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125320553</v>
+        <v>125320479</v>
       </c>
       <c r="B4" t="n">
-        <v>56537</v>
+        <v>56518</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,30 +954,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>6 registreringar av sång, ett antal födosöksbeteenden.</t>
+          <t>15 registreringar med sång, stort antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 23563-2023 artfynd.xlsx
+++ b/artfynd/A 23563-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125320553</v>
+        <v>125320520</v>
       </c>
       <c r="B2" t="n">
-        <v>56537</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -782,11 +773,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>04:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>6 registreringar av sång, ett antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,15 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125320520</v>
+        <v>125320553</v>
       </c>
       <c r="B3" t="n">
-        <v>56525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56538</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,26 +810,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -858,7 +839,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -916,6 +901,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>6 registreringar av sång, ett antal födosöksbeteenden.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,12 +935,7 @@
         <v>125320479</v>
       </c>
       <c r="B4" t="n">
-        <v>56518</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23563-2023 artfynd.xlsx
+++ b/artfynd/A 23563-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125320520</v>
       </c>
       <c r="B2" t="n">
-        <v>56526</v>
+        <v>56823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>125320553</v>
       </c>
       <c r="B3" t="n">
-        <v>56538</v>
+        <v>56835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>125320479</v>
       </c>
       <c r="B4" t="n">
-        <v>56519</v>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,6 +1062,444 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111285313</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Äng 205 m NV Väktorsjöarna 119, Sjöbacken, Hjärtum, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>327560</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6453571</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111285412</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vägkant 200 m VSV Väktorsjöarna 119, Sjöbacken, Hjärtum, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>327535</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6453429</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115629058</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skogssäter-Stenungsund-Ingelkärr, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>327560</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6453573</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Robert Petersen, Johanna Ek, Tilda Lindkvist, Jeanette Karlsson, Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115629059</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogssäter-Stenungsund-Ingelkärr, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>327575</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6453583</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Robert Petersen, Johanna Ek, Tilda Lindkvist, Jeanette Karlsson, Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23563-2023 artfynd.xlsx
+++ b/artfynd/A 23563-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125320520</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -929,6 +939,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125320553</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,6 +1077,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125320479</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1180,6 +1200,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111285313</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1298,6 +1323,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111285412</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1399,6 +1429,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629058</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,8 +1535,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629059</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>